--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,17 +601,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M-84D74F</t>
+          <t>M-E84260</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Assignment 14: LangGraph &amp; Agent Orchestration</t>
+          <t>Assignment 2: Data Structures &amp; Algorithms</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -629,24 +629,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-18 15:42:08</t>
+          <t>2026-05-18 15:48:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M-372E8D</t>
+          <t>M-4432CB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assignment 14: LangGraph &amp; Agent Orchestration</t>
+          <t>Assignment 2: Data Structures &amp; Algorithms</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -664,19 +664,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-18 15:42:09</t>
+          <t>2026-05-18 15:48:24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M-E84260</t>
+          <t>M-7229E0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -699,24 +699,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-18 15:48:23</t>
+          <t>2026-05-18 15:48:25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M-4432CB</t>
+          <t>M-FB2646</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assignment 2: Data Structures &amp; Algorithms</t>
+          <t>Assignment 4: Version Control &amp; Software Design</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -734,14 +734,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-18 15:48:24</t>
+          <t>2026-05-18 15:50:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M-7229E0</t>
+          <t>M-08D086</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assignment 2: Data Structures &amp; Algorithms</t>
+          <t>Assignment 7: Docker &amp; Infrastructure</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -769,19 +769,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-18 15:48:25</t>
+          <t>2026-05-18 17:06:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M-FB2646</t>
+          <t>M-BF6649</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -804,24 +804,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-18 15:50:50</t>
+          <t>2026-05-18 17:32:28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M-3F5859</t>
+          <t>M-BE9F41</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assignment 4: Version Control &amp; Software Design</t>
+          <t>Assignment 3: Systems &amp; Networking</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -839,24 +839,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-18 15:50:51</t>
+          <t>2026-05-19 14:04:43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M-08D086</t>
+          <t>M-66CC1F</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assignment 7: Docker &amp; Infrastructure</t>
+          <t>Assignment 10: Classical Machine Learning</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -874,42 +874,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-18 17:06:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>M-BF6649</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>L003</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Assignment 4: Version Control &amp; Software Design</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>C001</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-05-18 17:32:28</t>
+          <t>2026-05-19 14:24:09</t>
         </is>
       </c>
     </row>

--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,41 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>M-92244A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Assignment 4: Version Control &amp; Software Design</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:23:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -481,11 +481,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -621,15 +621,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026-05-18 15:48:23</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-05-19 18:49:01</t>
         </is>
       </c>
     </row>
@@ -726,11 +731,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>

--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,15 +481,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-05-18 15:36:44</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-05-21 11:33:49</t>
         </is>
       </c>
     </row>
@@ -910,6 +915,41 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-05-19 18:23:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M-A55A4F</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Assignment 8: Data Science &amp; Pandas</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-20 17:16:32</t>
         </is>
       </c>
     </row>

--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -481,15 +481,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026-05-18 15:36:44</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-05-19 19:09:46</t>
         </is>
       </c>
     </row>

--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-05-19 19:09:46</t>
+          <t>2026-05-21 17:54:35</t>
         </is>
       </c>
     </row>
@@ -591,15 +591,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026-05-18 15:42:07</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-05-21 16:41:09</t>
         </is>
       </c>
     </row>
@@ -731,7 +736,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -740,6 +745,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-05-18 15:50:50</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:45:12</t>
         </is>
       </c>
     </row>
@@ -915,6 +925,636 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-05-19 18:23:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>M-0FCC7D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Assignment 7: Docker &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:35:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M-36B5E4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Assignment 3: Systems &amp; Networking</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:48:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>M-113E5E</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Assignment 5: Relational Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:48:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>M-7149C6</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Assignment 6: API Development with FastAPI</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:48:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>M-D6FF23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Assignment 7: Docker &amp; Infrastructure</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:48:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>M-EA5A1D</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Assignment 8: Data Science &amp; Pandas</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:48:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>M-525CDC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Assignment 9: System Design &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:48:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>M-B06008</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Assignment 10: Classical Machine Learning</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:49:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>M-8651B7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:49:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>M-C573EB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Assignment 12: Prompt Engineering &amp; LLMsn</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:49:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>M-0D0361</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Assignment 13: Retrieval-Augmented Generation (RAG)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:49:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M-88B16A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>L001</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Assignment 15: Model Context Protocol (MCP)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:49:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>M-703E46</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Assignment 9: System Design &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:58:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>M-D338FF</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>L003</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Assignment 9: System Design &amp; Architecture</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:58:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>M-85F48D</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:59:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>M-38DD9B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>L003</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:59:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>M-5BDD2D</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>L002</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Assignment 5: Relational Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>M-034F62</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>L003</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Assignment 5: Relational Databases &amp; SQL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C001</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-05-21 18:59:11</t>
         </is>
       </c>
     </row>

--- a/data/storage/learner_assignments.xlsx
+++ b/data/storage/learner_assignments.xlsx
@@ -536,17 +536,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M-B34FDA</t>
+          <t>M-EA55A9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Assignment 1: Python Mastery &amp; OOP</t>
+          <t>Assignment 14: LangGraph &amp; Agent Orchestration</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,22 +556,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-18 15:39:43</t>
+          <t>2026-05-18 15:42:07</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-05-21 16:41:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M-EA55A9</t>
+          <t>M-E84260</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -581,7 +586,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Assignment 14: LangGraph &amp; Agent Orchestration</t>
+          <t>Assignment 2: Data Structures &amp; Algorithms</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -591,32 +596,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-18 15:42:07</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-05-21 16:41:09</t>
+          <t>2026-05-18 15:48:23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M-E84260</t>
+          <t>M-4432CB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -639,19 +639,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-18 15:48:23</t>
+          <t>2026-05-18 15:48:24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M-4432CB</t>
+          <t>M-7229E0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -674,24 +674,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-18 15:48:24</t>
+          <t>2026-05-18 15:48:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M-7229E0</t>
+          <t>M-FB2646</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Assignment 2: Data Structures &amp; Algorithms</t>
+          <t>Assignment 4: Version Control &amp; Software Design</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -709,24 +709,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-18 15:48:25</t>
+          <t>2026-05-18 15:50:50</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-05-21 17:45:12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M-FB2646</t>
+          <t>M-08D086</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Assignment 4: Version Control &amp; Software Design</t>
+          <t>Assignment 7: Docker &amp; Infrastructure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -736,7 +741,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -744,19 +749,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-18 15:50:50</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-05-21 17:45:12</t>
+          <t>2026-05-18 17:06:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M-08D086</t>
+          <t>M-BF6649</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Assignment 7: Docker &amp; Infrastructure</t>
+          <t>Assignment 4: Version Control &amp; Software Design</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -784,14 +784,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-05-18 17:06:50</t>
+          <t>2026-05-18 17:32:28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M-BF6649</t>
+          <t>M-BE9F41</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Assignment 4: Version Control &amp; Software Design</t>
+          <t>Assignment 3: Systems &amp; Networking</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -819,24 +819,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-18 17:32:28</t>
+          <t>2026-05-19 14:04:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M-BE9F41</t>
+          <t>M-66CC1F</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assignment 3: Systems &amp; Networking</t>
+          <t>Assignment 10: Classical Machine Learning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -854,14 +854,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-05-19 14:04:43</t>
+          <t>2026-05-19 14:24:09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M-66CC1F</t>
+          <t>M-92244A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Assignment 10: Classical Machine Learning</t>
+          <t>Assignment 4: Version Control &amp; Software Design</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -889,14 +889,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-19 14:24:09</t>
+          <t>2026-05-19 18:23:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M-92244A</t>
+          <t>M-0FCC7D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Assignment 4: Version Control &amp; Software Design</t>
+          <t>Assignment 7: Docker &amp; Infrastructure</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -924,24 +924,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-19 18:23:07</t>
+          <t>2026-05-21 18:35:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M-0FCC7D</t>
+          <t>M-36B5E4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Assignment 7: Docker &amp; Infrastructure</t>
+          <t>Assignment 3: Systems &amp; Networking</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -951,22 +951,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-21 18:35:15</t>
+          <t>2026-05-21 18:48:49</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:54:22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M-36B5E4</t>
+          <t>M-113E5E</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +981,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Assignment 3: Systems &amp; Networking</t>
+          <t>Assignment 5: Relational Databases &amp; SQL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -994,14 +999,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-21 18:48:49</t>
+          <t>2026-05-21 18:48:52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M-113E5E</t>
+          <t>M-7149C6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,7 +1016,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assignment 5: Relational Databases &amp; SQL</t>
+          <t>Assignment 6: API Development with FastAPI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1029,14 +1034,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-21 18:48:52</t>
+          <t>2026-05-21 18:48:54</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M-7149C6</t>
+          <t>M-D6FF23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,7 +1051,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Assignment 6: API Development with FastAPI</t>
+          <t>Assignment 7: Docker &amp; Infrastructure</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1064,14 +1069,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-21 18:48:54</t>
+          <t>2026-05-21 18:48:55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M-D6FF23</t>
+          <t>M-EA5A1D</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1086,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Assignment 7: Docker &amp; Infrastructure</t>
+          <t>Assignment 8: Data Science &amp; Pandas</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1099,14 +1104,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-21 18:48:55</t>
+          <t>2026-05-21 18:48:57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M-EA5A1D</t>
+          <t>M-525CDC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1121,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Assignment 8: Data Science &amp; Pandas</t>
+          <t>Assignment 9: System Design &amp; Architecture</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1134,14 +1139,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-21 18:48:57</t>
+          <t>2026-05-21 18:48:58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M-525CDC</t>
+          <t>M-B06008</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1156,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Assignment 9: System Design &amp; Architecture</t>
+          <t>Assignment 10: Classical Machine Learning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1169,14 +1174,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-21 18:48:58</t>
+          <t>2026-05-21 18:49:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M-B06008</t>
+          <t>M-8651B7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1191,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assignment 10: Classical Machine Learning</t>
+          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1204,14 +1209,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-05-21 18:49:00</t>
+          <t>2026-05-21 18:49:01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M-8651B7</t>
+          <t>M-C573EB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1226,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
+          <t>Assignment 12: Prompt Engineering &amp; LLMsn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1239,14 +1244,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-05-21 18:49:01</t>
+          <t>2026-05-21 18:49:03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M-C573EB</t>
+          <t>M-0D0361</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1261,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Assignment 12: Prompt Engineering &amp; LLMsn</t>
+          <t>Assignment 13: Retrieval-Augmented Generation (RAG)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1274,14 +1279,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-05-21 18:49:03</t>
+          <t>2026-05-21 18:49:05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M-0D0361</t>
+          <t>M-88B16A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1296,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Assignment 13: Retrieval-Augmented Generation (RAG)</t>
+          <t>Assignment 15: Model Context Protocol (MCP)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1309,24 +1314,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-21 18:49:05</t>
+          <t>2026-05-21 18:49:08</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M-88B16A</t>
+          <t>M-703E46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assignment 15: Model Context Protocol (MCP)</t>
+          <t>Assignment 9: System Design &amp; Architecture</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1344,19 +1349,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-21 18:49:08</t>
+          <t>2026-05-21 18:58:31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M-703E46</t>
+          <t>M-D338FF</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1379,24 +1384,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-05-21 18:58:31</t>
+          <t>2026-05-21 18:58:32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>M-D338FF</t>
+          <t>M-85F48D</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Assignment 9: System Design &amp; Architecture</t>
+          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1414,19 +1419,19 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-05-21 18:58:32</t>
+          <t>2026-05-21 18:59:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>M-85F48D</t>
+          <t>M-38DD9B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1449,24 +1454,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-05-21 18:59:07</t>
+          <t>2026-05-21 18:59:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>M-38DD9B</t>
+          <t>M-5BDD2D</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Assignment 11: Deep Learning &amp; PyTorch</t>
+          <t>Assignment 5: Relational Databases &amp; SQL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1484,19 +1489,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-05-21 18:59:08</t>
+          <t>2026-05-21 18:59:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>M-5BDD2D</t>
+          <t>M-034F62</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1519,14 +1524,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-05-21 18:59:10</t>
+          <t>2026-05-21 18:59:11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>M-034F62</t>
+          <t>M-73149D</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1541,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Assignment 5: Relational Databases &amp; SQL</t>
+          <t>Assignment 1: Python Mastery &amp; OOP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-05-21 18:59:11</t>
+          <t>2026-05-25 15:56:27</t>
         </is>
       </c>
     </row>
